--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513283_ELIMINGRC12FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513283_ELIMINGRC12FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4279</v>
+        <v>5.1535</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1195</v>
+        <v>6.1434</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6916</v>
+        <v>-0.9899</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1124</v>
+        <v>2.1918</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1612</v>
+        <v>2.2502</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0488</v>
+        <v>-0.0584</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0066</v>
+        <v>3.1957</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4047</v>
+        <v>2.5633</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6018</v>
+        <v>0.6323</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8941</v>
+        <v>-1.0038</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2435</v>
+        <v>-0.3131</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6506</v>
+        <v>-0.6907</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.975</v>
+        <v>0.6622</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4536</v>
+        <v>0.2261</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5214</v>
+        <v>0.4361</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1398</v>
+        <v>0.1574</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6593</v>
+        <v>2.7216</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.5195</v>
+        <v>-2.5642</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.889</v>
+        <v>1.7948</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6944</v>
+        <v>2.5787</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1947</v>
+        <v>-0.7839</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0523</v>
+        <v>2.4116</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6562</v>
+        <v>2.0582</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3961</v>
+        <v>0.3534</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0348</v>
+        <v>2.9313</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1872</v>
+        <v>2.299</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1524</v>
+        <v>0.6323</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0871</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8434</v>
+        <v>-0.2407</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2438</v>
+        <v>-0.2789</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0006</v>
+        <v>1.1684</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0006</v>
+        <v>1.1684</v>
       </c>
       <c r="S3" t="n">
-        <v>1.801</v>
+        <v>0.0464</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6804</v>
+        <v>-0.3525</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1206</v>
+        <v>0.3989</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1398</v>
+        <v>-1.8316</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9791</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8393</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1669</v>
+        <v>1.7714</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8102</v>
+        <v>2.2729</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6433</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4045</v>
+        <v>-0.967</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0602</v>
+        <v>-0.6106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3443</v>
+        <v>-0.3564</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8412</v>
+        <v>0.254</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2394</v>
+        <v>0.3183</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6018</v>
+        <v>-0.0643</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4367</v>
+        <v>-1.2209</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1792</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2575</v>
+        <v>-0.292</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2003</v>
+        <v>1.9474</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2003</v>
+        <v>1.9474</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3617</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.031</v>
+        <v>-0.0406</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3927</v>
+        <v>0.6742</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7997</v>
+        <v>0.1574</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.0595</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7997</v>
+        <v>-1.9021</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3571</v>
+        <v>0.9643</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2716</v>
+        <v>0.9062</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3844</v>
+        <v>-0.3913</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2069</v>
+        <v>-0.1934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1775</v>
+        <v>-0.1979</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2763</v>
+        <v>-0.2216</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3563</v>
+        <v>-0.3027</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1081</v>
+        <v>-0.1697</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1494</v>
+        <v>0.1093</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2575</v>
+        <v>-0.2789</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1416</v>
+        <v>-0.255</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1623</v>
+        <v>0.0323</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0208</v>
+        <v>-0.2873</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,31 +877,31 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.395</v>
+        <v>0.5527</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3312</v>
+        <v>-0.1482</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7262</v>
+        <v>0.7009</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4119</v>
+        <v>0.3588</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1374</v>
+        <v>-0.1663</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="J7" t="n">
-        <v>0.12</v>
+        <v>0.1232</v>
       </c>
       <c r="K7" t="n">
-        <v>0.12</v>
+        <v>0.1232</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2919</v>
+        <v>0.2356</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2574</v>
+        <v>-0.2895</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.497</v>
+        <v>-0.2681</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4512</v>
+        <v>-0.2713</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0458</v>
+        <v>0.0032</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0649</v>
+        <v>0.5238</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0245</v>
+        <v>-0.3841</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0405</v>
+        <v>0.9079</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2243</v>
+        <v>1.3314</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2643</v>
+        <v>0.3653</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04</v>
+        <v>0.9661</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04</v>
+        <v>1.4036</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.6902</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04</v>
+        <v>0.7134</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2643</v>
+        <v>-0.0722</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2643</v>
+        <v>-0.3249</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2527</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1807</v>
+        <v>-1.0023</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0645</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1163</v>
+        <v>-0.1883</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3401</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3401</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2927</v>
+        <v>-0.0544</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9015</v>
+        <v>-0.0213</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6088</v>
+        <v>-0.0331</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3717</v>
+        <v>-0.2371</v>
       </c>
       <c r="H9" t="n">
-        <v>0.405</v>
+        <v>-0.2776</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9667</v>
+        <v>0.0405</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3234</v>
+        <v>0.0405</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6818</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0483</v>
+        <v>-0.2776</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2366</v>
+        <v>-0.2776</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2849</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2003</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8645</v>
+        <v>-0.1484</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2247</v>
+        <v>-0.0618</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6398</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3311</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3546</v>
+        <v>-0.135</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8733</v>
+        <v>-1.0672</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5187</v>
+        <v>0.9322</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2725</v>
+        <v>0.1696</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2012</v>
+        <v>1.1196</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9286</v>
+        <v>-0.95</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2816</v>
+        <v>1.3366</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1597</v>
+        <v>1.1905</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1219</v>
+        <v>0.146</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.009</v>
+        <v>-1.167</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0415</v>
+        <v>-0.0709</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0505</v>
+        <v>-1.096</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0067</v>
+        <v>0.2727</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9334</v>
+        <v>-0.3212</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9267</v>
+        <v>0.5939</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4204</v>
+        <v>-0.3826</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7794</v>
+        <v>0.8384</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7716</v>
+        <v>-1.2804</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2567</v>
+        <v>-1.888</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4851</v>
+        <v>0.6076</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1154</v>
+        <v>-1.1287</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0843</v>
+        <v>-0.0929</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0311</v>
+        <v>-1.0358</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9361</v>
+        <v>-0.8985</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2981</v>
+        <v>-0.2745</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1793</v>
+        <v>-0.2302</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2138</v>
+        <v>0.1816</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.716</v>
+        <v>-0.2365</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.2953</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1358</v>
+        <v>0.0588</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2057</v>
+        <v>-2.4695</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-1.0667</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2637</v>
+        <v>-1.4028</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.876</v>
+        <v>-0.848</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3491</v>
+        <v>-1.3408</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4731</v>
+        <v>0.4929</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1105</v>
+        <v>-0.9994</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0343</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0762</v>
+        <v>-0.0322</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2345</v>
+        <v>0.1514</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3148</v>
+        <v>-0.3736</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1098</v>
+        <v>-0.1352</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.031</v>
+        <v>-0.3147</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1408</v>
+        <v>0.1795</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2394</v>
+        <v>-1.2916</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4392</v>
+        <v>-2.5126</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3928</v>
+        <v>-3.0997</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1758</v>
+        <v>-3.5352</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7829</v>
+        <v>0.4355</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6445</v>
+        <v>-2.6553</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8831</v>
+        <v>0.8246</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.5275</v>
+        <v>-3.4799</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6285</v>
+        <v>-1.5002</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1197</v>
+        <v>1.1495</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.7482</v>
+        <v>-2.6497</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0159</v>
+        <v>-1.1551</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2366</v>
+        <v>-0.3249</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7793</v>
+        <v>-0.8302</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1485</v>
+        <v>0.1661</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5467</v>
+        <v>-0.0877</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3982</v>
+        <v>0.2538</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.6177</v>
+        <v>-5.5698</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.2538</v>
+        <v>-6.2281</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6362</v>
+        <v>0.6583</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2321</v>
+        <v>-2.1728</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0556</v>
+        <v>0.0508</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.2877</v>
+        <v>-2.2236</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.4229</v>
+        <v>-2.2216</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2853</v>
+        <v>0.3875</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.7082</v>
+        <v>-2.6091</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1908</v>
+        <v>0.0488</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2297</v>
+        <v>-0.3367</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2648</v>
+        <v>-0.3539</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2891</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0243</v>
+        <v>0.2847</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.5795</v>
+        <v>-1.6226</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.864199999999998</v>
+        <v>-1.2404</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.4493</v>
+        <v>-2.677900000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5851</v>
+        <v>1.4374</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.356099999999999</v>
+        <v>-1.3291</v>
       </c>
       <c r="H15" t="n">
-        <v>4.068099999999999</v>
+        <v>3.9871</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.423999999999999</v>
+        <v>-5.3162</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8732</v>
+        <v>4.051500000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>6.4689</v>
+        <v>7.177099999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.595800000000001</v>
+        <v>-3.1258</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.228999999999999</v>
+        <v>-5.380400000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.4008</v>
+        <v>-3.1899</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8283</v>
+        <v>-2.1902</v>
       </c>
       <c r="P15" t="n">
-        <v>3.000700000000001</v>
+        <v>2.9212</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14.0041</v>
+        <v>-13.6316</v>
       </c>
       <c r="R15" t="n">
-        <v>17.0048</v>
+        <v>16.5526</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2891</v>
+        <v>-0.6183999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.8554</v>
+        <v>-2.9393</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5662</v>
+        <v>2.321</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.2201</v>
+        <v>-2.214</v>
       </c>
       <c r="W15" t="n">
-        <v>9.536799999999999</v>
+        <v>9.841700000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-11.7568</v>
+        <v>-12.0557</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. VINALLONGA BLANCO</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4924</v>
+        <v>2.6973</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8098</v>
+        <v>1.5813</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6826</v>
+        <v>1.116</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1908</v>
+        <v>4.5379</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0172</v>
+        <v>0.2129</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1737</v>
+        <v>4.325</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2851</v>
+        <v>4.0496</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8031</v>
+        <v>-0.295</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.518</v>
+        <v>4.3447</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.09420000000000001</v>
+        <v>0.4883</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7859</v>
+        <v>0.508</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6917</v>
+        <v>-0.0197</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2001</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0003</v>
+        <v>-2.921</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7614</v>
+        <v>-0.0958</v>
       </c>
       <c r="T16" t="n">
-        <v>1.525</v>
+        <v>-0.1578</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2364</v>
+        <v>0.0621</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2598</v>
+        <v>0.3973</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2598</v>
+        <v>-0.2133</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6452</v>
+        <v>2.6969</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7576</v>
+        <v>0.9915</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8875999999999999</v>
+        <v>1.7053</v>
       </c>
       <c r="G17" t="n">
-        <v>4.5019</v>
+        <v>2.6198</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2381</v>
+        <v>2.0137</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2638</v>
+        <v>0.6061</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9251</v>
+        <v>3.188</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3181</v>
+        <v>3.2202</v>
       </c>
       <c r="L17" t="n">
-        <v>4.2432</v>
+        <v>-0.0322</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5768</v>
+        <v>-0.5682</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5562</v>
+        <v>-1.2065</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0206</v>
+        <v>0.6383</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.2006</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8002</v>
+        <v>1.9474</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.2365</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2335</v>
+        <v>-0.4965</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2977</v>
+        <v>0.26</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4081</v>
+        <v>1.2873</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5999</v>
+        <v>1.2211</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1918</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.372</v>
+        <v>2.4474</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8596</v>
+        <v>2.407</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5123</v>
+        <v>0.0405</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1332</v>
+        <v>-0.1413</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1382</v>
+        <v>-0.1103</v>
       </c>
       <c r="I18" t="n">
-        <v>0.005</v>
+        <v>-0.031</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7034</v>
+        <v>0.7836</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5834</v>
+        <v>0.662</v>
       </c>
       <c r="L18" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8366</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7216</v>
+        <v>-0.7723</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.115</v>
+        <v>-0.1526</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4254</v>
+        <v>0.4845</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7023</v>
+        <v>-0.3719</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1278</v>
+        <v>0.8565</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4799</v>
+        <v>2.4937</v>
       </c>
       <c r="W18" t="n">
-        <v>3.8591</v>
+        <v>3.9426</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3793</v>
+        <v>-1.449</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0661</v>
+        <v>1.9429</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4272</v>
+        <v>1.0491</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6389</v>
+        <v>0.8938</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5661</v>
+        <v>1.2184</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9369</v>
+        <v>1.0695</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6292</v>
+        <v>0.149</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9684</v>
+        <v>1.4118</v>
       </c>
       <c r="K19" t="n">
-        <v>3.0446</v>
+        <v>1.9142</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0762</v>
+        <v>-0.5024</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4022</v>
+        <v>-0.1933</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1077</v>
+        <v>-0.8447</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7054</v>
+        <v>0.6514</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.0003</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0009</v>
+        <v>-0.9737</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0006</v>
+        <v>0.7789</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7675</v>
+        <v>1.1986</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.74</v>
+        <v>0.611</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0275</v>
+        <v>0.5877</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2678</v>
+        <v>-0.2795</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.068</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0304</v>
+        <v>0.4756</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.401</v>
+        <v>-1.4932</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4314</v>
+        <v>1.9688</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3347</v>
+        <v>-1.4005</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4421</v>
+        <v>-1.4553</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1074</v>
+        <v>0.0548</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.7835</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9343</v>
+        <v>-0.8646</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4804</v>
+        <v>-0.617</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5078</v>
+        <v>-0.5907</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0274</v>
+        <v>-0.0262</v>
       </c>
       <c r="P20" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2965</v>
+        <v>-0.1375</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5467</v>
+        <v>-0.7097</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.5722</v>
       </c>
       <c r="V20" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2047,28 +2047,28 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5218</v>
+        <v>-0.1699</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2715</v>
+        <v>-1.0235</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7497</v>
+        <v>0.8536</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3431</v>
+        <v>0.2798</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1138</v>
+        <v>0.079</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2293</v>
+        <v>0.2008</v>
       </c>
       <c r="J22" t="n">
-        <v>0.18</v>
+        <v>0.1837</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1</v>
+        <v>0.1026</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1631</v>
+        <v>0.0961</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0138</v>
+        <v>-0.0236</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2648</v>
+        <v>0.1345</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4512</v>
+        <v>-0.2335</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1864</v>
+        <v>0.368</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8053</v>
+        <v>-0.4983</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.31</v>
+        <v>-0.0183</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4953</v>
+        <v>-0.48</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1668</v>
+        <v>-0.1598</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8623</v>
+        <v>-0.86</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6955</v>
+        <v>0.7003</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0056</v>
+        <v>0.0823</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6762</v>
+        <v>-0.6311</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6818</v>
+        <v>0.7134</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1724</v>
+        <v>-0.242</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1861</v>
+        <v>-0.2289</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.239</v>
+        <v>0.1036</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3156</v>
+        <v>-0.1006</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0766</v>
+        <v>0.2042</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2326</v>
+        <v>-1.4748</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.804</v>
+        <v>-0.4133</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5714</v>
+        <v>-1.0614</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8449</v>
+        <v>-0.8213</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.043</v>
+        <v>-1.7176</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1981</v>
+        <v>0.8963</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1069</v>
+        <v>-0.0359</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4708</v>
+        <v>-0.0282</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6361</v>
+        <v>-0.0077</v>
       </c>
       <c r="M24" t="n">
-        <v>0.262</v>
+        <v>-0.7853</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5722</v>
+        <v>-1.6894</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.9041</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8005</v>
+        <v>0.9737</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.0009</v>
+        <v>-0.9737</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2003</v>
+        <v>1.9474</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8253</v>
+        <v>-0.1267</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3247</v>
+        <v>-0.6248</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5006</v>
+        <v>0.4981</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5876</v>
+        <v>-1.5005</v>
       </c>
       <c r="W24" t="n">
-        <v>1.9791</v>
+        <v>1.2211</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3915</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0978</v>
+        <v>-1.8483</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4155</v>
+        <v>-1.8458</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6823</v>
+        <v>-0.0025</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7277</v>
+        <v>-0.8106</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6301</v>
+        <v>-0.9888</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9023</v>
+        <v>0.1782</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1325</v>
+        <v>-0.9252</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0582</v>
+        <v>-0.3257</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0743</v>
+        <v>-0.5995</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5953000000000001</v>
+        <v>0.1146</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.5719</v>
+        <v>-0.6631</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9766</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>1.0003</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0003</v>
+        <v>-2.921</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0006</v>
+        <v>1.1684</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9108000000000001</v>
+        <v>0.0897</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4825</v>
+        <v>-0.0591</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5717</v>
+        <v>0.1488</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4596</v>
+        <v>0.6252</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1998</v>
+        <v>2.0595</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.6593</v>
+        <v>-1.4343</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.3841</v>
+        <v>-4.7179</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5974</v>
+        <v>-2.0383</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.7867</v>
+        <v>-2.6795</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.3385</v>
+        <v>-4.3015</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.5582</v>
+        <v>-2.538</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.7803</v>
+        <v>-1.7635</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.0446</v>
+        <v>-2.8818</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.9725</v>
+        <v>-0.8722</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.0721</v>
+        <v>-2.0096</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.2939</v>
+        <v>-1.4196</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.5857</v>
+        <v>-1.6658</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2918</v>
+        <v>0.2461</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7732</v>
+        <v>-0.1779</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4111</v>
+        <v>-0.1781</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3622</v>
+        <v>0.0002</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3278</v>
+        <v>0.3457</v>
       </c>
       <c r="W26" t="n">
-        <v>3.8591</v>
+        <v>3.9426</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.5313</v>
+        <v>-3.597</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.864400000000002</v>
+        <v>1.858799999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.645299999999999</v>
+        <v>-0.4956</v>
       </c>
       <c r="F27" t="n">
-        <v>4.509599999999999</v>
+        <v>2.3546</v>
       </c>
       <c r="G27" t="n">
-        <v>1.356</v>
+        <v>1.3288</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.068</v>
+        <v>-3.987</v>
       </c>
       <c r="I27" t="n">
-        <v>5.423999999999999</v>
+        <v>5.316000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>4.229200000000001</v>
+        <v>5.3805</v>
       </c>
       <c r="K27" t="n">
-        <v>2.400899999999999</v>
+        <v>3.1901</v>
       </c>
       <c r="L27" t="n">
-        <v>1.8283</v>
+        <v>2.1905</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.8731</v>
+        <v>-4.0513</v>
       </c>
       <c r="N27" t="n">
-        <v>-6.468900000000001</v>
+        <v>-7.177</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5957</v>
+        <v>3.1258</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="Q27" t="n">
-        <v>-17.0051</v>
+        <v>-16.5525</v>
       </c>
       <c r="R27" t="n">
-        <v>14.004</v>
+        <v>13.6315</v>
       </c>
       <c r="S27" t="n">
-        <v>1.2891</v>
+        <v>1.2365</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.5662</v>
+        <v>-2.321</v>
       </c>
       <c r="U27" t="n">
-        <v>3.855299999999999</v>
+        <v>3.5578</v>
       </c>
       <c r="V27" t="n">
-        <v>2.22</v>
+        <v>2.2143</v>
       </c>
       <c r="W27" t="n">
-        <v>12.6968</v>
+        <v>12.9974</v>
       </c>
       <c r="X27" t="n">
-        <v>-10.4768</v>
+        <v>-10.7834</v>
       </c>
     </row>
   </sheetData>
